--- a/data/trans_orig/IP31KM08_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM08_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>12458</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8195</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17236</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,28%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>21,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>46,04%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>19365</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14516</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>24739</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>53,21%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9416</t>
+          <t>13227</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18680</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>32926</t>
+          <t>30456</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26189</t>
+          <t>23896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40041</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>46,57%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24977</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>20199</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>29240</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,72%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>53,96%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>78,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27130</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21756</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>31979</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>58,35%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>68,78%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>24683</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>26605</t>
+          <t>20103</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35869</t>
+          <t>29454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>70,05%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,21%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>49660</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51738</t>
+          <t>42806</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65590</t>
+          <t>56220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>61,98%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>70,17%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,107 +1063,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>81781</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>71858</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91800</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>52,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>58,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>74221</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>63146</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>83723</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>46,59%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>39,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>52,56%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92944</t>
+          <t>68328</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82420</t>
+          <t>59823</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>105034</t>
+          <t>78673</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>46,95%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>54,06%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>150109</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>137066</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>164023</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>49,61%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>45,3%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>57,72%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>167165</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>150422</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>181588</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>48,98%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>44,08%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>85078</t>
+          <t>75261</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75576</t>
+          <t>65242</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96153</t>
+          <t>85184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,67 +1216,67 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>89015</t>
+          <t>77190</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76925</t>
+          <t>66845</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99539</t>
+          <t>85695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>53,05%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
+          <t>58,89%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>152451</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>138537</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>165494</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>50,39%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>45,79%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
           <t>54,7%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>174094</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>159671</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>190837</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>51,02%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>46,79%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83680</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>70537</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>96677</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>41,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>35,25%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>48,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>78922</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>66706</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>90202</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>45,6%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>52,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87384</t>
+          <t>81345</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73599</t>
+          <t>70043</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>102314</t>
+          <t>92157</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>166306</t>
+          <t>165025</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146829</t>
+          <t>147308</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>185349</t>
+          <t>182277</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,07%</t>
+          <t>48,63%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>116446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>103449</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>129589</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>58,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>51,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>64,75%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>94150</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>82870</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>106366</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>54,4%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>47,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>61,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125106</t>
+          <t>93327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>110176</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>138891</t>
+          <t>104629</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>219257</t>
+          <t>209773</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>200214</t>
+          <t>192521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238734</t>
+          <t>227490</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>60,7%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>136346</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>116072</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>151853</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>39,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>51,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>109580</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>76635</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>129304</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>39,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>47,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>139887</t>
+          <t>119285</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118357</t>
+          <t>104998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>157994</t>
+          <t>134353</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>249467</t>
+          <t>255631</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212543</t>
+          <t>233282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>280403</t>
+          <t>279647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>155875</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>140368</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>176149</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,34%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>48,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>164687</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>144963</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>197632</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>60,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>52,85%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>165112</t>
+          <t>136052</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>147005</t>
+          <t>120984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>186642</t>
+          <t>150339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>329799</t>
+          <t>291927</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>298863</t>
+          <t>267911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366723</t>
+          <t>314276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>57,4%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>416</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>314265</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>289722</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>339438</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>45,76%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>42,18%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>49,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>406</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>282089</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>240513</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>305116</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>43,19%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>36,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>46,72%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>333776</t>
+          <t>286956</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>305651</t>
+          <t>265036</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>361634</t>
+          <t>307614</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>46,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>41,04%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>615865</t>
+          <t>601221</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>570122</t>
+          <t>565196</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>653213</t>
+          <t>633148</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>372559</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>347386</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>397102</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>54,24%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>57,82%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>371045</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>348018</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>412621</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>56,81%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>53,28%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>63,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>524</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>410957</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>383099</t>
+          <t>310594</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>439082</t>
+          <t>353172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>50,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>782002</t>
+          <t>703810</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>744654</t>
+          <t>671883</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>827745</t>
+          <t>739835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>51,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
